--- a/01_Poziadavky/funkcionalne-poziadavky.xlsx
+++ b/01_Poziadavky/funkcionalne-poziadavky.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Papo\source\repos\Rocnikovy_stick_fight\dokumentacia\Stickops\01_Poziadavky\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4C283CB-2EB2-469A-A55B-F66567395E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CE8B9C2-D1E5-443B-84D9-AB67A74CFBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{280D526C-C131-43F4-A80B-A2F654BC155C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D79FA002-75F3-47E0-97D3-3658A4B966BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Funkcionálne" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -53,16 +53,13 @@
     <t>MoSCoW</t>
   </si>
   <si>
-    <t>Stav (16. 10. 2026)</t>
-  </si>
-  <si>
     <t>Hlavné menu a nastavenia</t>
   </si>
   <si>
     <t>FR-001</t>
   </si>
   <si>
-    <t>Systém musí po spustení zobraziť hlavné menu s voľbami HRAŤ (Kampaň, Rýchly zápas, Posledný replay), KOZMETIKA, NASTAVENIA a KONIEC.</t>
+    <t>Systém musí po spustení zobraziť hlavné menu s voľbami Kampaň, Rýchly zápas, Posledný replay, Kozmetika, Nastavenia a Koniec.</t>
   </si>
   <si>
     <t>Hráč</t>
@@ -71,19 +68,16 @@
     <t>M</t>
   </si>
   <si>
-    <t>Hotové</t>
-  </si>
-  <si>
     <t>FR-002</t>
   </si>
   <si>
-    <t>Systém musí umožniť ovládať všetky menu klávesnicou (šípky, Enter, Esc = späť).</t>
+    <t>Systém musí umožniť ovládať všetky menu klávesnicou.</t>
   </si>
   <si>
     <t>FR-003</t>
   </si>
   <si>
-    <t>Systém by mal umožniť ovládať menu aj myšou (kliknutie, pravý klik = späť).</t>
+    <t>Systém by mal umožniť ovládať menu aj myšou.</t>
   </si>
   <si>
     <t>S</t>
@@ -92,27 +86,24 @@
     <t>FR-004</t>
   </si>
   <si>
-    <t>Systém by mal umožniť nastaviť hlasitosť hudby a zvukov a zapamätať si ju (game/saves/settings.json).</t>
+    <t>Systém by mal umožniť nastaviť hlasitosť hudby a zvukov a zapamätať si ju pri ďalšom spustení.</t>
   </si>
   <si>
     <t>FR-005</t>
   </si>
   <si>
-    <t>Systém by mal umožniť prepnúť celú obrazovku (NASTAVENIA alebo F11).</t>
+    <t>Systém by mal umožniť prepínať medzi celou obrazovkou a oknom.</t>
   </si>
   <si>
     <t>FR-006</t>
   </si>
   <si>
-    <t>Systém by mohol umožniť zmeniť priradenie kláves pre akcie.</t>
+    <t>Systém by mohol umožniť zmeniť priradenie kláves pre jednotlivé herné akcie.</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>Čiastočne – iba úpravou content/settings/input.json, nie v menu</t>
-  </si>
-  <si>
     <t>FR-007</t>
   </si>
   <si>
@@ -122,133 +113,193 @@
     <t>W</t>
   </si>
   <si>
-    <t>Zámerne nerealizované</t>
-  </si>
-  <si>
-    <t>Boj</t>
+    <t>Boj – pohyb</t>
   </si>
   <si>
     <t>FR-008</t>
   </si>
   <si>
-    <t>Systém musí umožniť pohyb postavy: chôdzu (A/D), skok (Space) s dvojskokom a odrazom od steny a lezenie po plošinkách arény.</t>
+    <t>Systém musí umožniť pohyb bojovníka: chôdzu, skok, dvojskok, odraz od steny a vyskočenie na plošinky arény.</t>
+  </si>
+  <si>
+    <t>Boj – útoky</t>
   </si>
   <si>
     <t>FR-009</t>
   </si>
   <si>
-    <t>Systém musí umožniť ľahký útok (J, kombo jab → cross → hák), ťažký útok (K) a kop (L) so smerovými variantmi (W hore, S dole, dopredu, vo vzduchu).</t>
+    <t>Systém musí poskytovať tri druhy útokov: ľahký úder, ťažký úder a kop.</t>
   </si>
   <si>
     <t>FR-010</t>
   </si>
   <si>
-    <t>Systém musí umožniť blok (Ctrl) na načasovanie: perfektný blok zruší poškodenie, útočníka zapotáca a dá SILU; skorší blok prepustí časť poškodenia.</t>
+    <t>Systém by mal meniť útok podľa smeru, ktorý hráč drží (hore, dole, dopredu, vo vzduchu) – napr. uppercut, podrazenie, výpad.</t>
   </si>
   <si>
     <t>FR-011</t>
   </si>
   <si>
-    <t>Systém by mal umožniť úhyb (Shift): skrčenie, úskok dopredu, záklon dozadu, s možnosťou hneď zaútočiť.</t>
+    <t>Systém musí umožniť kombo: opakovaný ľahký úder po zásahu pokračuje reťazou troch úderov; po zásahu sa dá nadviazať ťažkým úderom alebo kopom. Každý ďalší zásah v kombe uberá menej (škálovanie).</t>
   </si>
   <si>
     <t>FR-012</t>
   </si>
   <si>
-    <t>Systém by mal umožniť chmat (J + K), klinč (I) a skok nohami napred (O).</t>
+    <t>Systém by mal pri každom útoku rozlišovať fázy príprava – aktívna fáza – zotavenie; minutý útok nechá útočníka chvíľu otvoreného.</t>
+  </si>
+  <si>
+    <t>Boj – obrana</t>
   </si>
   <si>
     <t>FR-013</t>
   </si>
   <si>
-    <t>Systém by mal mať ukazovateľ SILY (3 dieliky), ktorý sa plní iba hrou; ô + útok vykoná posilnený (ohnivý) úder.</t>
+    <t>Systém musí umožniť blok, ktorý funguje iba proti útoku spredu.</t>
   </si>
   <si>
     <t>FR-014</t>
   </si>
   <si>
-    <t>Systém musí vyhodnocovať zásahy podľa zásahových zón, škálovať poškodenie v kombe a odpočítavať zdravie.</t>
+    <t>Systém musí vyhodnocovať načasovanie bloku: perfektný blok (tesne pred zásahom) zruší poškodenie, útočníka zapotáca a dá obrancovi SILU; čím skôr bol blok začatý, tým viac poškodenia prejde.</t>
   </si>
   <si>
     <t>FR-015</t>
   </si>
   <si>
-    <t>Systém musí počas boja zobrazovať zdravie a SILU oboch bojovníkov, čas kola, vyhraté kolá a označenie TY / AI.</t>
+    <t>Systém by mal zabrániť zneužitiu bloku: po pustení bloku sa chvíľu nedá znova blokovať.</t>
   </si>
   <si>
     <t>FR-016</t>
   </si>
   <si>
-    <t>Systém musí ukončiť kolo knockoutom alebo uplynutím času a vyhlásiť víťaza zápasu po potrebnom počte kôl.</t>
+    <t>Systém by mal umožniť úhyb (na mieste, dopredu, dozadu): krátka nezraniteľnosť, potom zraniteľná medzera a čas do ďalšieho úhybu.</t>
+  </si>
+  <si>
+    <t>Boj – zásahy a časti tela</t>
   </si>
   <si>
     <t>FR-017</t>
   </si>
   <si>
-    <t>Systém by mal po poslednom kole automaticky prehrať finisher víťaza (filmová scéna).</t>
+    <t>Systém musí rozdeliť telo bojovníka na zásahové zóny: hlava, trup a nohy.</t>
   </si>
   <si>
     <t>FR-018</t>
   </si>
   <si>
-    <t>Systém musí umožniť pozastaviť hru (Esc) s ponukou Pokračovať, Odznova, Ovládanie, Hlavné menu, Ukončiť hru.</t>
+    <t>Systém musí zásahové zóny ohodnotiť: zásah do hlavy uberá viac a omráči dlhšie, zásah do trupu je základný, zásah do nôh uberá menej, ale nízky útok môže súpera podraziť.</t>
   </si>
   <si>
     <t>FR-019</t>
   </si>
   <si>
-    <t>Systém by mohol každý dohraný zápas uložiť ako replay (seed + vstupy) a prehrať posledný replay z menu.</t>
+    <t>Systém musí pri zásahu odpočítať zdravie, krátko omráčiť zasiahnutého (hitstun) a odsunúť ho; po veľkom kombe ho zrazí na zem, kde je chvíľu nezraniteľný a potom vstane.</t>
   </si>
   <si>
     <t>FR-020</t>
   </si>
   <si>
+    <t>Systém by mal obmedziť žonglovanie súpera vo vzduchu (každý ďalší zásah vo vzduchu omráči kratšie), aby nevzniklo nekonečné kombo.</t>
+  </si>
+  <si>
+    <t>Boj – špeciálne akcie</t>
+  </si>
+  <si>
+    <t>FR-021</t>
+  </si>
+  <si>
+    <t>Systém by mal umožniť chmat (nedá sa zablokovať, dá sa mu uhnúť), klinč (prejde cez blok, preruší ho rýchly úder) a skok nohami napred (prebije ľahké údery).</t>
+  </si>
+  <si>
+    <t>FR-022</t>
+  </si>
+  <si>
+    <t>Systém by mal mať ukazovateľ SILY s tromi dielikmi, ktorý sa plní iba hrou (zásahy, utŕžené rany, perfektný blok); posilnený útok minie SILU, bez SILY sa vykoná bežný útok.</t>
+  </si>
+  <si>
+    <t>Boj – kolá a zápas</t>
+  </si>
+  <si>
+    <t>FR-023</t>
+  </si>
+  <si>
+    <t>Systém musí počas boja zobrazovať zdravie a SILU oboch bojovníkov, čas kola, vyhraté kolá a označenie, ktorá postava patrí hráčovi.</t>
+  </si>
+  <si>
+    <t>FR-024</t>
+  </si>
+  <si>
+    <t>Systém musí ukončiť kolo knockoutom alebo uplynutím času (vyhrá bojovník s viac zdravím) a vyhlásiť víťaza zápasu po potrebnom počte vyhratých kôl.</t>
+  </si>
+  <si>
+    <t>FR-025</t>
+  </si>
+  <si>
+    <t>Systém by mal po poslednom kole automaticky prehrať finisher víťaza (krátka filmová scéna).</t>
+  </si>
+  <si>
+    <t>FR-026</t>
+  </si>
+  <si>
+    <t>Systém musí umožniť pozastaviť zápas s ponukou Pokračovať, Odznova, Ovládanie, Hlavné menu a Ukončiť hru.</t>
+  </si>
+  <si>
+    <t>FR-027</t>
+  </si>
+  <si>
+    <t>Systém by mohol každý dohraný zápas uložiť ako záznam (replay) a prehrať ho.</t>
+  </si>
+  <si>
+    <t>FR-028</t>
+  </si>
+  <si>
     <t>Systém by mohol podporovať ovládanie gamepadom.</t>
   </si>
   <si>
     <t>Herné režimy</t>
   </si>
   <si>
-    <t>FR-021</t>
-  </si>
-  <si>
-    <t>Systém musí umožniť rýchly zápas s výberom súpera (osobnosť AI alebo druhý hráč) a arény.</t>
-  </si>
-  <si>
-    <t>FR-022</t>
-  </si>
-  <si>
-    <t>Systém by mal umožniť zápas dvoch hráčov na jednej klávesnici.</t>
+    <t>FR-029</t>
+  </si>
+  <si>
+    <t>Systém musí umožniť rýchly zápas s výberom súpera (úroveň AI, porazený boss alebo druhý hráč) a arény.</t>
+  </si>
+  <si>
+    <t>FR-030</t>
+  </si>
+  <si>
+    <t>Systém by mal umožniť zápas dvoch hráčov na jednom počítači.</t>
   </si>
   <si>
     <t>Druhý hráč</t>
   </si>
   <si>
-    <t>FR-023</t>
-  </si>
-  <si>
-    <t>Systém by mal obsahovať kampaň s 25 levelmi v 5 kapitolách (Tréningová hala, Strechy, Dojo, Noc v meste, Reaktor), kde každý piaty level je boss.</t>
-  </si>
-  <si>
-    <t>FR-024</t>
-  </si>
-  <si>
-    <t>Systém by mal ukladať postup v kampani (ai/saves/progress.json), po výhre odomknúť ďalší level a umožniť postup zmazať (podržať DELETE).</t>
-  </si>
-  <si>
-    <t>FR-025</t>
-  </si>
-  <si>
-    <t>Systém by mohol v kampani ponúkať presily (2–4 súperi po sebe) a výzvy (menej zdravia, plná SILA, krátky čas).</t>
-  </si>
-  <si>
-    <t>FR-026</t>
-  </si>
-  <si>
-    <t>Systém by mohol za výhry odomykať údery SILY a finishery bossov a v menu KOZMETIKA umožniť vybrať finisher so živým náhľadom.</t>
-  </si>
-  <si>
-    <t>FR-027</t>
+    <t>FR-031</t>
+  </si>
+  <si>
+    <t>Systém by mal obsahovať kampaň s 25 levelmi v 5 kapitolách, kde každý piaty level je boss.</t>
+  </si>
+  <si>
+    <t>FR-032</t>
+  </si>
+  <si>
+    <t>Systém by mal ukladať postup v kampani, po výhre odomknúť ďalší level a umožniť postup zmazať.</t>
+  </si>
+  <si>
+    <t>FR-033</t>
+  </si>
+  <si>
+    <t>Systém by mohol v kampani ponúkať presily (viac súperov po sebe bez obnovy zdravia) a výzvy (menej zdravia, plná SILA, krátky čas).</t>
+  </si>
+  <si>
+    <t>FR-034</t>
+  </si>
+  <si>
+    <t>Systém by mohol za výhry odomykať posilnené útoky a finishery bossov a umožniť vybrať si finisher (Kozmetika).</t>
+  </si>
+  <si>
+    <t>FR-035</t>
   </si>
   <si>
     <t>Systém nebude podporovať hru cez internet.</t>
@@ -257,49 +308,43 @@
     <t>Umelá inteligencia</t>
   </si>
   <si>
-    <t>FR-028</t>
-  </si>
-  <si>
-    <t>Systém musí ovládať AI súpera rovnakými povelmi, aké má hráč (AI nepodvádza).</t>
+    <t>FR-036</t>
+  </si>
+  <si>
+    <t>Systém musí ovládať AI súpera rovnakými povelmi, aké má hráč, a AI musí vidieť hru s reakčným oneskorením (nepodvádza).</t>
   </si>
   <si>
     <t>AI protivník</t>
   </si>
   <si>
-    <t>FR-029</t>
-  </si>
-  <si>
-    <t>Systém musí ponúkať súperov rôznej obtiažnosti (14 osobností AI, tempo podľa kapitoly kampane).</t>
-  </si>
-  <si>
-    <t>Hotové – obtiažnosť sa volí súperom, nie samostatným prepínačom</t>
-  </si>
-  <si>
-    <t>FR-030</t>
-  </si>
-  <si>
-    <t>Systém by mal používať natrénované modely 5 bossov (Hromotĺk, Bašta, Sokol, Zmija, Víchor), každý s vlastným štýlom.</t>
-  </si>
-  <si>
-    <t>FR-031</t>
-  </si>
-  <si>
-    <t>Systém by mal umožniť tréning AI bez grafiky a uložiť model do súboru (.policy.json).</t>
+    <t>FR-037</t>
+  </si>
+  <si>
+    <t>Systém musí ponúkať 3 úrovne obtiažnosti bežných AI súperov – Ľahká, Stredná, Ťažká – ktoré sa líšia reakčným časom, presnosťou bloku a agresivitou.</t>
+  </si>
+  <si>
+    <t>FR-038</t>
+  </si>
+  <si>
+    <t>Systém by mal mať 5 bossov ako samostatnú kategóriu nad tromi úrovňami: každého ovláda natrénovaná neurónová sieť s vlastným štýlom; bossovia sa objavia na konci každej kapitoly kampane a v rýchlom zápase sú dostupní až po porazení.</t>
+  </si>
+  <si>
+    <t>FR-039</t>
+  </si>
+  <si>
+    <t>Systém by mal umožniť tréning bossov bez grafiky (napodobnenie skriptovaného súpera + neuroevolúcia) a uložiť natrénovaný model do súboru.</t>
   </si>
   <si>
     <t>Vývojár AI</t>
   </si>
   <si>
-    <t>Hotové (stick_trainer.exe, stick_cli.exe, Python)</t>
-  </si>
-  <si>
-    <t>FR-032</t>
-  </si>
-  <si>
-    <t>Systém by mohol počas tréningu zobrazovať štatistiky a robiť turnaje osobností s HTML reportom.</t>
-  </si>
-  <si>
-    <t>FR-033</t>
+    <t>FR-040</t>
+  </si>
+  <si>
+    <t>Systém by mohol počas tréningu zobrazovať štatistiky (úspešnosť, odmena po generáciách) a robiť turnaje súperov s reportom.</t>
+  </si>
+  <si>
+    <t>FR-041</t>
   </si>
   <si>
     <t>Systém nebude trénovať AI počas hrania u hráča.</t>
@@ -308,67 +353,64 @@
     <t>Herný obsah</t>
   </si>
   <si>
-    <t>FR-034</t>
-  </si>
-  <si>
-    <t>Systém musí načítať postavy, útoky, pózy, finishery, arény, efekty, kampaň a osobnosti AI zo súborov JSON (game/content, ai/content).</t>
+    <t>FR-042</t>
+  </si>
+  <si>
+    <t>Systém musí načítať bojovníka, útoky, finishery, arény, kampaň a súperov AI zo súborov JSON.</t>
   </si>
   <si>
     <t>Tvorca obsahu</t>
   </si>
   <si>
-    <t>FR-035</t>
+    <t>FR-043</t>
   </si>
   <si>
     <t>Systém musí pri chybe v obsahu zobraziť hlášku po slovensky so súborom, riadkom a návrhom opravy.</t>
   </si>
   <si>
-    <t>FR-036</t>
-  </si>
-  <si>
-    <t>Systém musí kontrolovať rozsahy hodnôt a odkazy medzi súbormi (schémy v _schemas).</t>
-  </si>
-  <si>
-    <t>FR-037</t>
-  </si>
-  <si>
-    <t>Systém by mal v JSON povoliť komentáre a kódovanie UTF-8 s BOM.</t>
-  </si>
-  <si>
-    <t>FR-038</t>
-  </si>
-  <si>
-    <t>Systém by mohol po úprave obsahu načítať zmeny bez reštartu (F5).</t>
-  </si>
-  <si>
-    <t>FR-039</t>
-  </si>
-  <si>
-    <t>Systém nebude obsahovať grafický editor postáv ani arén.</t>
+    <t>FR-044</t>
+  </si>
+  <si>
+    <t>Systém musí kontrolovať povolené rozsahy hodnôt a odkazy medzi súbormi.</t>
+  </si>
+  <si>
+    <t>FR-045</t>
+  </si>
+  <si>
+    <t>Systém by mal v súboroch obsahu povoliť komentáre a kódovanie UTF-8 s BOM.</t>
+  </si>
+  <si>
+    <t>FR-046</t>
+  </si>
+  <si>
+    <t>Systém by mohol načítať zmeny obsahu bez reštartu hry.</t>
+  </si>
+  <si>
+    <t>FR-047</t>
+  </si>
+  <si>
+    <t>Systém nebude obsahovať grafický editor bojovníkov ani arén.</t>
   </si>
   <si>
     <t>Zvuk a ladenie</t>
   </si>
   <si>
-    <t>FR-040</t>
+    <t>FR-048</t>
   </si>
   <si>
     <t>Systém by mal prehrávať zvuky úderov, blokov a knockoutu a hudbu v menu, v boji a vo finále.</t>
   </si>
   <si>
-    <t>Hotové (SoLoud)</t>
-  </si>
-  <si>
-    <t>FR-041</t>
+    <t>FR-049</t>
   </si>
   <si>
     <t>Systém by mohol prelínať hudbu a stlmiť ju v pauze.</t>
   </si>
   <si>
-    <t>FR-042</t>
-  </si>
-  <si>
-    <t>Systém by mohol mať ladiace nástroje: F1 hitboxy, F2 spomalenie, F3 ladiaci panel.</t>
+    <t>FR-050</t>
+  </si>
+  <si>
+    <t>Systém by mohol mať ladiace nástroje: zobrazenie zásahových zón, spomalenie a panel s hodnotami.</t>
   </si>
 </sst>
 </file>
@@ -792,18 +834,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6864B67D-6E18-4E91-A70A-BE1AB7382838}">
-  <dimension ref="A1:E49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F50824-EA43-4A80-B187-DDA637F8ED15}">
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="80.7109375" customWidth="1"/>
+    <col min="2" max="2" width="90.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,780 +857,796 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="C40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="C42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2" t="s">
+      <c r="C44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="D48" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="C51" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="D53" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C54" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>10</v>
+      <c r="B55" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>